--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-10T08:30:16.277Z</t>
+    <t>2026-09-10T12:43:39.456Z</t>
   </si>
   <si>
     <t>Merkle - We Power the Experience Economy</t>
